--- a/LISTEN/Script/23_12_n3/23_12.xlsx
+++ b/LISTEN/Script/23_12_n3/23_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\23_12_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3805B39-0F9B-4C68-8A4F-98D026DF4FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814CF8B6-DD2C-4A77-9295-1D9681909627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="201">
   <si>
     <t>Fre</t>
   </si>
@@ -156,10 +156,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>接受；获得;顶在头上</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>第一</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -413,6 +409,430 @@
   </si>
   <si>
     <t>へいてん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>得到、领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>座位；席位；职位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地板；地面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ファミレス</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家庭餐厅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>がっかり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>失望，颓丧，筋疲力尽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>楽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>らく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>楽しい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>快乐的，愉快的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻松、舒服、简单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>増える</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>この前</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近，上次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>車椅子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>くるまいす</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轮椅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>計画</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けいかく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>これから</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从现在起；今后；接下来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もっと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更加；进一步</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>感激</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんげき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>感激；感动；感恩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>映画館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えいがかん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>興味</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうみ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最も</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もっとも</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>派手</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はで</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>华丽；艳丽；花哨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歩く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あるく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>走；步行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>りゅうこう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>がら</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花样；花纹；图案</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かっこいい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>帅气的; 有型的; 酷的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>底</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そこ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>底部；深处；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>連絡先</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>联系方式；联络地址</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>着方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きかた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用方法；穿着方式；做法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>着物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>和服</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だいたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>観光地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんこうち</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>温泉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おんせん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>忘れ物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>わすれもの</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>代</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>代替；辈分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いえ/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>うち</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寝坊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ねぼう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡懒觉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遅れ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おくれ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟；落后；晚点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>待ち合わせ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まちあわせ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>约定会面；约会</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遅刻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちこく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>息子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>むすこ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>娘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>むすめ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自宅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じたく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>代表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だいひょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集める</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あつめる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>画家</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>がか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えがく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>絵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>え</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>画；图画；绘画</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飾る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かざる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装饰；装点；修饰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>社長</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゃちょう</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -420,7 +840,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,6 +860,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -972,7 +1399,7 @@
         <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.15">
@@ -980,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
@@ -991,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
@@ -1002,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
@@ -1016,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
@@ -1027,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
@@ -1038,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.15">
@@ -1049,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
@@ -1060,10 +1487,13 @@
         <v>0</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>51</v>
+      <c r="D23" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
@@ -1071,13 +1501,13 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.15">
@@ -1085,13 +1515,13 @@
         <v>0</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.15">
@@ -1099,10 +1529,10 @@
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
@@ -1110,10 +1540,13 @@
         <v>0</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>61</v>
+      <c r="D27" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
@@ -1121,10 +1554,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
@@ -1132,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
@@ -1146,13 +1579,13 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
@@ -1160,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
@@ -1171,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
@@ -1182,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
@@ -1193,10 +1626,10 @@
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1204,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1218,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1229,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
@@ -1240,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
@@ -1251,13 +1684,13 @@
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1265,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1276,13 +1709,13 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -1290,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -1301,28 +1734,30 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
@@ -1339,9 +1774,525 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/LISTEN/Script/23_12_n3/23_12.xlsx
+++ b/LISTEN/Script/23_12_n3/23_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\23_12_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814CF8B6-DD2C-4A77-9295-1D9681909627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5DF6AB-3700-4B71-925D-4FD157C54E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="279">
   <si>
     <t>Fre</t>
   </si>
@@ -833,6 +833,318 @@
   </si>
   <si>
     <t>しゃちょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>癖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>くせ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>习惯；毛病；特征</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正しい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ただしい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正确；准确；正当</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡単</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんたん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>否定的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひていてき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>消极的，否定的；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>言い方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いいかた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>说法；表达方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>質問</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しつもん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提问；询问；疑问</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二つ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふたつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>それとも</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>或者；还是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>半分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はん ぶん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>コップ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯子；玻璃杯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不足している</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぶそくしている</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>変化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>へんか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>種類</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅるい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>池</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いけ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じんこう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不足</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふそく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不够；不足；短缺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>少ない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すくない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>少；不多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜辺り</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜あたり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附近；周围；一带；大约</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>影響</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えいきょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>環境</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんきょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しぜん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>土地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とち</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せいかつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人々</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひとびと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人们</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>農業</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>のうぎょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>専門家</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんもんか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>专家；专业人员</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大変さ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>困难程度；辛苦程度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>方法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほうほう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しばらく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时；不久；好久；暂且</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうらい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>就職</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅうしょく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>時代</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じだい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>働く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はたらく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>広告</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こうこく</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2298,14 +2610,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
-    <col min="4" max="4" width="32.125" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="2" customWidth="1"/>
+    <col min="2" max="3" width="23.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
@@ -2320,6 +2632,410 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/23_12_n3/23_12.xlsx
+++ b/LISTEN/Script/23_12_n3/23_12.xlsx
@@ -461,95 +461,95 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>何とかなる</t>
+          <t>前方</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>总会有办法的</t>
+          <t>ぜんぽう</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>出席者</t>
+          <t>降る</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>しゅっせきしゃ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ふる</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>下（雨、雪等）；降临；发生</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>閉店</t>
+          <t>出席者</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>へいてん</t>
+          <t>しゅっせきしゃ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>切手</t>
+          <t>閉店</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>きって</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>邮票;邮票券</t>
-        </is>
-      </c>
+          <t>へいてん</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>返信</t>
+          <t>床</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>へんしん</t>
+          <t>ゆか</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>回信；回复</t>
+          <t>地板；地面</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -573,15 +573,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>前方</t>
+          <t>切手</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ぜんぽう</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>きって</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>邮票;邮票券</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -589,19 +593,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>降る</t>
+          <t>何とかなる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ふる</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>下（雨、雪等）；降临；发生</t>
-        </is>
-      </c>
+          <t>总会有办法的</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -609,15 +609,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>相談</t>
+          <t>濡れる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>そうだん</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ぬれる</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>湿；淋湿；浸湿</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -625,12 +629,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>関係者</t>
+          <t>相談</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>かんけいしゃ</t>
+          <t>そうだん</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -641,19 +645,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>濡れる</t>
+          <t>関係者</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ぬれる</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>湿；淋湿；浸湿</t>
-        </is>
-      </c>
+          <t>かんけいしゃ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -661,19 +661,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>床</t>
+          <t>拭く</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ゆか</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>地板；地面</t>
-        </is>
-      </c>
+          <t>ふく</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -681,12 +677,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>拭く</t>
+          <t>観光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>かんこう</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -697,15 +693,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>観光</t>
+          <t>返信</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>かんこう</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>へんしん</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>回信；回复</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -713,15 +713,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>降りる</t>
+          <t>頂く</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>おりる</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>いただく</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>得到、领取</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -729,12 +733,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>到着</t>
+          <t>集まる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>とうちゃく</t>
+          <t>あつまる</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -745,17 +749,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>お城</t>
+          <t>席</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>おしろ</t>
+          <t>せき</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>城堡；城郭；城楼</t>
+          <t>座位；席位；职位</t>
         </is>
       </c>
     </row>
@@ -765,12 +769,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>見学</t>
+          <t>配る</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>けんがく</t>
+          <t>くばる</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -781,12 +785,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>場所</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>だいいち</t>
+          <t>ばしょ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -797,12 +801,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>急に</t>
+          <t>決まって</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>きゅうに</t>
+          <t>きまって</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -813,19 +817,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>頂く</t>
+          <t>降りる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>いただく</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>得到、领取</t>
-        </is>
-      </c>
+          <t>おりる</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -833,19 +833,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>日時</t>
+          <t>急に</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>にちじ</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>日期；时间</t>
-        </is>
-      </c>
+          <t>きゅうに</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -853,12 +849,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>決まって</t>
+          <t>第一</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>きまって</t>
+          <t>だいいち</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -869,12 +865,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>場所</t>
+          <t>見学</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ばしょ</t>
+          <t>けんがく</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -885,15 +881,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>配る</t>
+          <t>お城</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>くばる</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>おしろ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>城堡；城郭；城楼</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -901,19 +901,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>席</t>
+          <t>到着</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>せき</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>座位；席位；职位</t>
-        </is>
-      </c>
+          <t>とうちゃく</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -921,15 +917,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>集まる</t>
+          <t>日時</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>あつまる</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>にちじ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>日期；时间</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -953,12 +953,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>靴</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>くつ</t>
+          <t>よる</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -989,12 +989,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>今朝</t>
+          <t>靴</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>けさ</t>
+          <t>くつ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1005,19 +1005,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>授業</t>
+          <t>昼食</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>じゅぎょう</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>上课，授课</t>
-        </is>
-      </c>
+          <t>ちゅうしょく</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1025,19 +1021,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>送る</t>
+          <t>本屋</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>おくる</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>寄送；传递；度过</t>
-        </is>
-      </c>
+          <t>书店；书局</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1045,12 +1037,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>メモ</t>
+          <t>セーター</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>备忘录</t>
+          <t>毛衣</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1061,15 +1053,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>研究家</t>
+          <t>鞄</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>けんきゅうか</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>かばん</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>书包</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>歴史</t>
+          <t>客</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>れきし</t>
+          <t>きゃく</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1093,12 +1089,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>研究家</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>よる</t>
+          <t>けんきゅうか</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1109,19 +1105,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>鞄</t>
+          <t>メモ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>かばん</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>书包</t>
-        </is>
-      </c>
+          <t>备忘录</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1129,15 +1121,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>セーター</t>
+          <t>送る</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>毛衣</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>おくる</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>寄送；传递；度过</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1145,15 +1141,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>本屋</t>
+          <t>授業</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>书店；书局</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>じゅぎょう</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>上课，授课</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>昼食</t>
+          <t>今朝</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ちゅうしょく</t>
+          <t>けさ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>客</t>
+          <t>歴史</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>きゃく</t>
+          <t>れきし</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1252,179 +1252,183 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ファミレス</t>
+          <t>飾る</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>家庭餐厅</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>かざる</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>装饰；装点；修饰</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>着物</t>
+          <t>感激</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>和服</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>かんげき</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>感激；感动；感恩</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>感激</t>
+          <t>底</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>かんげき</t>
+          <t>そこ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>感激；感动；感恩</t>
+          <t>底部；深处；</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>がっかり</t>
+          <t>描く</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>失望，颓丧，筋疲力尽</t>
+          <t>えがく</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>飾る</t>
+          <t>楽</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>かざる</t>
+          <t>らく</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>装饰；装点；修饰</t>
+          <t>轻松、舒服、简单</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>描く</t>
+          <t>かっこいい</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>えがく</t>
+          <t>帅气的; 有型的; 酷的</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>画家</t>
+          <t>流行</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>がか</t>
+          <t>りゅうこう</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>楽</t>
+          <t>柄</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>らく</t>
+          <t>がら</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>轻松、舒服、简单</t>
+          <t>花样；花纹；图案</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>流行</t>
+          <t>画家</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>りゅうこう</t>
+          <t>がか</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>柄</t>
+          <t>がっかり</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>がら</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>花样；花纹；图案</t>
-        </is>
-      </c>
+          <t>失望，颓丧，筋疲力尽</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1432,12 +1436,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>ファミレス</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>かんこうち</t>
+          <t>家庭餐厅</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1448,19 +1452,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>底</t>
+          <t>観光地</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>そこ</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>底部；深处；</t>
-        </is>
-      </c>
+          <t>かんこうち</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>かっこいい</t>
+          <t>着物</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>帅气的; 有型的; 酷的</t>
+          <t>和服</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>この前</t>
+          <t>もっと</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>最近，上次</t>
+          <t>更加；进一步</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>車椅子</t>
+          <t>着方</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>くるまいす</t>
+          <t>きかた</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>使用方法；穿着方式；做法</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>計画</t>
+          <t>連絡先</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>けいかく</t>
+          <t>联系方式；联络地址</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1536,19 +1536,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>派手</t>
+          <t>興味</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>はで</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>华丽；艳丽；花哨</t>
-        </is>
-      </c>
+          <t>きょうみ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1556,15 +1552,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>最も</t>
+          <t>歩く</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>もっとも</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>あるく</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>走；步行</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>これから</t>
+          <t>映画館</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>从现在起；今后；接下来</t>
+          <t>えいがかん</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>もっと</t>
+          <t>この前</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>更加；进一步</t>
+          <t>最近，上次</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>映画館</t>
+          <t>これから</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>えいがかん</t>
+          <t>从现在起；今后；接下来</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>増える</t>
+          <t>最も</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ふえる</t>
+          <t>もっとも</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1636,17 +1636,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>歩く</t>
+          <t>派手</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>あるく</t>
+          <t>はで</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>走；步行</t>
+          <t>华丽；艳丽；花哨</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>興味</t>
+          <t>計画</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>きょうみ</t>
+          <t>けいかく</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1672,15 +1672,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>連絡先</t>
+          <t>車椅子</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>联系方式；联络地址</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>くるまいす</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>轮椅</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1688,17 +1692,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>着方</t>
+          <t>待ち合わせ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>きかた</t>
+          <t>まちあわせ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>使用方法；穿着方式；做法</t>
+          <t>约定会面；约会</t>
         </is>
       </c>
     </row>
@@ -1724,19 +1728,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>待ち合わせ</t>
+          <t>自宅</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>まちあわせ</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>约定会面；约会</t>
-        </is>
-      </c>
+          <t>じたく</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>温泉</t>
+          <t>増える</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>おんせん</t>
+          <t>ふえる</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1776,19 +1776,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>代</t>
+          <t>温泉</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>だい</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>代替；辈分</t>
-        </is>
-      </c>
+          <t>おんせん</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1796,15 +1792,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>絵</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>いえ/うち</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>え</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>画；图画；绘画</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1812,19 +1812,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>寝坊</t>
+          <t>集める</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ねぼう</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>睡懒觉</t>
-        </is>
-      </c>
+          <t>あつめる</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1832,19 +1828,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>遅れ</t>
+          <t>代表</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>おくれ</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>延迟；落后；晚点</t>
-        </is>
-      </c>
+          <t>だいひょう</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1852,12 +1844,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>息子</t>
+          <t>娘</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>むすこ</t>
+          <t>むすめ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1868,12 +1860,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>遅刻</t>
+          <t>大体</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ちこく</t>
+          <t>だいたい</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1884,12 +1876,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>娘</t>
+          <t>息子</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>むすめ</t>
+          <t>むすこ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1900,15 +1892,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>自宅</t>
+          <t>遅れ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>じたく</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>おくれ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>延迟；落后；晚点</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1916,15 +1912,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>代表</t>
+          <t>寝坊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>だいひょう</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>ねぼう</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>睡懒觉</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>集める</t>
+          <t>家</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>あつめる</t>
+          <t>いえ/うち</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1948,17 +1948,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>絵</t>
+          <t>代</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>え</t>
+          <t>だい</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>画；图画；绘画</t>
+          <t>代替；辈分</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>大体</t>
+          <t>遅刻</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>だいたい</t>
+          <t>ちこく</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2038,240 +2038,228 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>苦手</t>
+          <t>環境</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>にがて</t>
+          <t>かんきょう</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>早退</t>
+          <t>間貸</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>そうたい</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>提早下班</t>
-        </is>
-      </c>
+          <t>まがし</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>生活</t>
+          <t>苦手</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>せいかつ</t>
+          <t>にがて</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>不足している</t>
+          <t>土地</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ぶそくしている</t>
+          <t>とち</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>否定的</t>
+          <t>旅館</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ひていてき</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>消极的，否定的；</t>
-        </is>
-      </c>
+          <t>りょかん</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>人工</t>
+          <t>飲食</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>じんこう</t>
+          <t>いんしょく</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>不足</t>
+          <t>早退</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ふそく</t>
+          <t>そうたい</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>不够；不足；短缺</t>
+          <t>提早下班</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>スーツ</t>
+          <t>広告</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>西装；套装</t>
+          <t>こうこく</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〜辺り</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>〜あたり</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>附近；周围；一带；大约</t>
-        </is>
-      </c>
+          <t>かみなり</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>農業</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>えいきょう</t>
+          <t>のうぎょう</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>間貸</t>
+          <t>人工</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>まがし</t>
+          <t>じんこう</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>スーツ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>かんきょう</t>
+          <t>西装；套装</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>土地</t>
+          <t>生活</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>とち</t>
+          <t>せいかつ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>飲食</t>
+          <t>不足している</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>いんしょく</t>
+          <t>ぶそくしている</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2282,15 +2270,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>コップ</t>
+          <t>鳴る</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杯子；玻璃杯</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>なる</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>(非生物)鸣，响</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,17 +2290,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>お伝えになる</t>
+          <t>否定的</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>尊敬：伝える</t>
+          <t>ひていてき</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>传达；转告；告知</t>
+          <t>消极的，否定的；</t>
         </is>
       </c>
     </row>
@@ -2318,15 +2310,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>それとも</t>
+          <t>お伝えになる</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>或者；还是</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>尊敬：伝える</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>传达；转告；告知</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2334,15 +2330,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>応募</t>
+          <t>〜辺り</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>おうぼ</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>〜あたり</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>附近；周围；一带；大约</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2350,15 +2350,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>緊張</t>
+          <t>不足</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>きんちょう</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>ふそく</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>不够；不足；短缺</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2366,12 +2370,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>歓迎会</t>
+          <t>影響</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>かんげいかい</t>
+          <t>えいきょう</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2382,12 +2386,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>就職</t>
+          <t>コップ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>しゅうしょく</t>
+          <t>杯子；玻璃杯</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2398,19 +2402,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>開会</t>
+          <t>緊張</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>かいかい</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>开幕</t>
-        </is>
-      </c>
+          <t>きんちょう</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>働く</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>かみなり</t>
+          <t>はたらく</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2434,19 +2434,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鳴る</t>
+          <t>就職</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>なる</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>(非生物)鸣，响</t>
-        </is>
-      </c>
+          <t>しゅうしょく</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2454,12 +2450,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>旅館</t>
+          <t>歓迎会</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>りょかん</t>
+          <t>かんげいかい</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2470,15 +2466,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>農業</t>
+          <t>開会</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>のうぎょう</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>かいかい</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>开幕</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>広告</t>
+          <t>応募</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>こうこく</t>
+          <t>おうぼ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>働く</t>
+          <t>それとも</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>はたらく</t>
+          <t>或者；还是</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2518,17 +2518,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>専門家</t>
+          <t>癖</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>せんもんか</t>
+          <t>くせ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>专家；专业人员</t>
+          <t>习惯；毛病；特征</t>
         </is>
       </c>
     </row>
@@ -2538,15 +2538,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>変化</t>
+          <t>専門家</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>へんか</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>せんもんか</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>专家；专业人员</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2554,12 +2558,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>種類</t>
+          <t>変化</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>しゅるい</t>
+          <t>へんか</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2570,19 +2574,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>少ない</t>
+          <t>種類</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>すくない</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>少；不多</t>
-        </is>
-      </c>
+          <t>しゅるい</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2590,15 +2590,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>大変さ</t>
+          <t>少ない</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>困难程度；辛苦程度</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>すくない</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>少；不多</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2606,19 +2610,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>人々</t>
+          <t>大変さ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ひとびと</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>人们</t>
-        </is>
-      </c>
+          <t>困难程度；辛苦程度</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2626,15 +2626,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>自然</t>
+          <t>人々</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>しぜん</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>ひとびと</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>人们</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2642,19 +2646,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>癖</t>
+          <t>自然</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>くせ</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>习惯；毛病；特征</t>
-        </is>
-      </c>
+          <t>しぜん</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2742,15 +2742,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>しばらく</t>
+          <t>ちっとも</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>暂时；不久；好久；暂且</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>一点也不；毫不；丝毫不</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>接否定</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2774,12 +2778,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ロビー</t>
+          <t>しばらく</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>大厅；门厅</t>
+          <t>暂时；不久；好久；暂且</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2790,17 +2794,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ちっとも</t>
+          <t>言い方</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>一点也不；毫不；丝毫不</t>
+          <t>いいかた</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>接否定</t>
+          <t>说法；表达方式</t>
         </is>
       </c>
     </row>
@@ -2810,12 +2814,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>経済</t>
+          <t>簡単</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>けいざい</t>
+          <t>かんたん</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2826,19 +2830,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>出る</t>
+          <t>池</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>でる</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>离开；参加</t>
-        </is>
-      </c>
+          <t>いけ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2846,15 +2846,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>帰る</t>
+          <t>正しい</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>返回</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>ただしい</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>正确；准确；正当</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2878,17 +2882,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>正しい</t>
+          <t>質問</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ただしい</t>
+          <t>しつもん</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>正确；准确；正当</t>
+          <t>提问；询问；疑问</t>
         </is>
       </c>
     </row>
@@ -2898,15 +2902,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>池</t>
+          <t>出る</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>いけ</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>でる</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>离开；参加</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2914,12 +2922,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>経済</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>かんたん</t>
+          <t>けいざい</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -2930,19 +2938,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>言い方</t>
+          <t>ロビー</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>いいかた</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>说法；表达方式</t>
-        </is>
-      </c>
+          <t>大厅；门厅</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2950,19 +2954,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>質問</t>
+          <t>帰る</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>しつもん</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>提问；询问；疑问</t>
-        </is>
-      </c>
+          <t>返回</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">

--- a/LISTEN/Script/23_12_n3/23_12.xlsx
+++ b/LISTEN/Script/23_12_n3/23_12.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -477,59 +477,63 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>降る</t>
+          <t>外に</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ふる</t>
+          <t>そとに</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>下（雨、雪等）；降临；发生</t>
+          <t>外部；外面；户外</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>出席者</t>
+          <t>降る</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>しゅっせきしゃ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>ふる</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>下（雨、雪等）；降临；发生</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>閉店</t>
+          <t>出席者</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>へいてん</t>
+          <t>しゅっせきしゃ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -549,41 +553,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>外に</t>
+          <t>閉店</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>そとに</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>外部；外面；户外</t>
-        </is>
-      </c>
+          <t>へいてん</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>切手</t>
+          <t>濡れる</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>きって</t>
+          <t>ぬれる</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>邮票;邮票券</t>
+          <t>湿；淋湿；浸湿</t>
         </is>
       </c>
     </row>
@@ -593,15 +593,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>何とかなる</t>
+          <t>切手</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>总会有办法的</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>きって</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>邮票;邮票券</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -609,19 +613,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>濡れる</t>
+          <t>何とかなる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ぬれる</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>湿；淋湿；浸湿</t>
-        </is>
-      </c>
+          <t>总会有办法的</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -645,12 +645,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>関係者</t>
+          <t>観光</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>かんけいしゃ</t>
+          <t>かんこう</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -661,15 +661,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>拭く</t>
+          <t>返信</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ふく</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>へんしん</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>回信；回复</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -677,12 +681,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>観光</t>
+          <t>関係者</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>かんこう</t>
+          <t>かんけいしゃ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -693,39 +697,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>返信</t>
+          <t>到着</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>へんしん</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>回信；回复</t>
-        </is>
-      </c>
+          <t>とうちゃく</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>頂く</t>
+          <t>拭く</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>いただく</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>得到、领取</t>
-        </is>
-      </c>
+          <t>ふく</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -733,12 +729,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>集まる</t>
+          <t>降りる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>あつまる</t>
+          <t>おりる</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -749,17 +745,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>席</t>
+          <t>日時</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>せき</t>
+          <t>にちじ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>座位；席位；职位</t>
+          <t>日期；时间</t>
         </is>
       </c>
     </row>
@@ -769,15 +765,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>配る</t>
+          <t>お城</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>くばる</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>おしろ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>城堡；城郭；城楼</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -785,12 +785,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>場所</t>
+          <t>見学</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ばしょ</t>
+          <t>けんがく</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -801,12 +801,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>決まって</t>
+          <t>第一</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>きまって</t>
+          <t>だいいち</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -817,15 +817,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>降りる</t>
+          <t>頂く</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>おりる</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>いただく</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>得到、领取</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -833,12 +837,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>急に</t>
+          <t>決まって</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>きゅうに</t>
+          <t>きまって</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -849,12 +853,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>場所</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>だいいち</t>
+          <t>ばしょ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -865,12 +869,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>見学</t>
+          <t>配る</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>けんがく</t>
+          <t>くばる</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -881,17 +885,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>お城</t>
+          <t>席</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>おしろ</t>
+          <t>せき</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>城堡；城郭；城楼</t>
+          <t>座位；席位；职位</t>
         </is>
       </c>
     </row>
@@ -901,12 +905,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>到着</t>
+          <t>集まる</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>とうちゃく</t>
+          <t>あつまる</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -917,19 +921,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日時</t>
+          <t>急に</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>にちじ</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>日期；时间</t>
-        </is>
-      </c>
+          <t>きゅうに</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -953,12 +953,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>研究家</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>よる</t>
+          <t>けんきゅうか</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -989,12 +989,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>靴</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>くつ</t>
+          <t>よる</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>昼食</t>
+          <t>今朝</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ちゅうしょく</t>
+          <t>けさ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1021,15 +1021,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>本屋</t>
+          <t>授業</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>书店；书局</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>じゅぎょう</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>上课，授课</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1037,15 +1041,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>セーター</t>
+          <t>送る</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>毛衣</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>おくる</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>寄送；传递；度过</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1053,19 +1061,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>鞄</t>
+          <t>メモ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>かばん</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>书包</t>
-        </is>
-      </c>
+          <t>备忘录</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1073,12 +1077,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>客</t>
+          <t>歴史</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>きゃく</t>
+          <t>れきし</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1089,15 +1093,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>研究家</t>
+          <t>鞄</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>けんきゅうか</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>かばん</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>书包</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1105,12 +1113,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>メモ</t>
+          <t>セーター</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>备忘录</t>
+          <t>毛衣</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1121,19 +1129,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>送る</t>
+          <t>本屋</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>おくる</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>寄送；传递；度过</t>
-        </is>
-      </c>
+          <t>书店；书局</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1141,19 +1145,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>授業</t>
+          <t>昼食</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>じゅぎょう</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>上课，授课</t>
-        </is>
-      </c>
+          <t>ちゅうしょく</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>今朝</t>
+          <t>靴</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>けさ</t>
+          <t>くつ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>歴史</t>
+          <t>客</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>れきし</t>
+          <t>きゃく</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
